--- a/vault-dalarna-university/04 ISLL/Analys/Innehåll.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Innehåll.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Innehåll" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GAR38K</t>
+          <t>GAR34X</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -725,24 +725,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Modulrubrik utan hp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (606 tecken): Kursen består av tre moduler. Modulerna _Språkfärdighet 1_ och _Språkfärdighet 2_ bygger på varandra. I modulerna introd…</t>
+          <t>Modulrubrik utan hp-angivelse: 'modul 1'</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR34X</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GAR38L</t>
+          <t>GAR38K</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (632 tecken): Kursen består av tre moduler. Modulen _Språkfärdighet 2 _bygger på färdigheter från _Språkfärdighet 1_. I båda modulerna…</t>
+          <t>6 meningar i ett stycke (606 tecken): Kursen består av tre moduler. Modulerna _Språkfärdighet 1_ och _Språkfärdighet 2_ bygger på varandra. I modulerna introd…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38K</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GAR38M</t>
+          <t>GAR38L</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (734 tecken): Kursen är uppbyggd runt tre moduler. Modulerna _Grammatik och textläsning_ samt _Muntlig språkfärdighet _samläses; modul…</t>
+          <t>7 meningar i ett stycke (632 tecken): Kursen består av tre moduler. Modulen _Språkfärdighet 2 _bygger på färdigheter från _Språkfärdighet 1_. I båda modulerna…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38L</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GAR38N</t>
+          <t>GAR38M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (698 tecken): Kursen innehåller tre moduler: _Grammatik och textläsning_, _Muntlig kommunikation_ och _Den arabiska litteraturens utve…</t>
+          <t>7 meningar i ett stycke (734 tecken): Kursen är uppbyggd runt tre moduler. Modulerna _Grammatik och textläsning_ samt _Muntlig språkfärdighet _samläses; modul…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GAR39M</t>
+          <t>GAR38N</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (525 tecken): Kursen introducerar det ekokritiska fältet inom litteraturvetenskap och kopplar samman dessa teoretiska texter med arabi…</t>
+          <t>5 meningar i ett stycke (698 tecken): Kursen innehåller tre moduler: _Grammatik och textläsning_, _Muntlig kommunikation_ och _Den arabiska litteraturens utve…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR38N</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>GAR39M</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1361 tecken): Kursen fokuserar på hur litteratur på engelska från 1989 till idag har behandlat migration och klimatförändring som två …</t>
+          <t>4 meningar i ett stycke (525 tecken): Kursen introducerar det ekokritiska fältet inom litteraturvetenskap och kopplar samman dessa teoretiska texter med arabi…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR39M</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AEN25H</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (646 tecken): I kursen studeras och problematiseras aktuell engelskdidaktisk forskning utifrån bland annat vetenskapsteoretiska perspe…</t>
+          <t>7 meningar i ett stycke (1361 tecken): Kursen fokuserar på hur litteratur på engelska från 1989 till idag har behandlat migration och klimatförändring som två …</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AEN25J</t>
+          <t>AEN25H</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -924,14 +924,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AEN25S</t>
+          <t>AEN25J</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1142 tecken): Kursen tematiserar betydelsefulla moderna teorier inom litteraturstudier på engelska och fokuserar på dessa teoriers inv…</t>
+          <t>6 meningar i ett stycke (646 tecken): I kursen studeras och problematiseras aktuell engelskdidaktisk forskning utifrån bland annat vetenskapsteoretiska perspe…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AEN26E</t>
+          <t>AEN25S</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (662 tecken): Kursen fokuserar på en fördjupande analys och tillämpning av den litterära forskningsprocessen. Kursen inriktar sig särs…</t>
+          <t>8 meningar i ett stycke (1142 tecken): Kursen tematiserar betydelsefulla moderna teorier inom litteraturstudier på engelska och fokuserar på dessa teoriers inv…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25S</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AEN299</t>
+          <t>AEN26E</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (1128 tecken): Kursens syfte är att, med utgångspunkt i relevanta teoretiska och metodologiska praktiker, kritiskt analysera begreppet …</t>
+          <t>6 meningar i ett stycke (662 tecken): Kursen fokuserar på en fördjupande analys och tillämpning av den litterära forskningsprocessen. Kursen inriktar sig särs…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN26E</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AEN29A</t>
+          <t>AEN299</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (824 tecken): Denna kurs omfattar kritiska studier av ett representativt urval av engelskspråkiga litterära verk som berör konflikt oc…</t>
+          <t>5 meningar i ett stycke (1128 tecken): Kursens syfte är att, med utgångspunkt i relevanta teoretiska och metodologiska praktiker, kritiskt analysera begreppet …</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN299</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AEN29C</t>
+          <t>AEN29A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (482 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
+          <t>4 meningar i ett stycke (824 tecken): Denna kurs omfattar kritiska studier av ett representativt urval av engelskspråkiga litterära verk som berör konflikt oc…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AEN2BT</t>
+          <t>AEN29C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (417 tecken): I kursen läses ett urval av skönlitterära texter på originalspråk. Texterna väljs av den studerande i samråd med läraren…</t>
+          <t>4 meningar i ett stycke (482 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AEN2BT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (969 tecken): Kursen behandlar centrala frågor rörande politik i samtida Afrika, där politik förstås som de antaganden och principer s…</t>
+          <t>4 meningar i ett stycke (417 tecken): I kursen läses ett urval av skönlitterära texter på originalspråk. Texterna väljs av den studerande i samråd med läraren…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AEN2BX</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på den euroasiatiska kontinenten. Ett antal centr…</t>
+          <t>5 meningar i ett stycke (969 tecken): Kursen behandlar centrala frågor rörande politik i samtida Afrika, där politik förstås som de antaganden och principer s…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AEN2BY</t>
+          <t>AEN2BX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på de amerikanska kontinenterna. Ett antal centra…</t>
+          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på den euroasiatiska kontinenten. Ett antal centr…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>AEN2BY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (955 tecken): Kursen fokuserar på jämförande litteraturvetenskaplig analys av migrationstematur ett diakront perspektiv. Kursen spegla…</t>
+          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på de amerikanska kontinenterna. Ett antal centra…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (600 tecken): Kursen inleds med en genomgång av den litteraturvetenskapliga forskningsprocessen, inbegripet ämnesval, problemställning…</t>
+          <t>6 meningar i ett stycke (955 tecken): Kursen fokuserar på jämförande litteraturvetenskaplig analys av migrationstematur ett diakront perspektiv. Kursen spegla…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EN2033</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (737 tecken): Under kursens gång prövar vi hypoteser om språk på grundval av autentiska data och undersöker, genom datorbaserade verkt…</t>
+          <t>4 meningar i ett stycke (600 tecken): Kursen inleds med en genomgång av den litteraturvetenskapliga forskningsprocessen, inbegripet ämnesval, problemställning…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EN2034</t>
+          <t>EN2033</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1089 tecken): Denna kurs är en introduktion till centrala typer av språkvetenskaplig dataanalys. Studenterna kommer att lära sig om bå…</t>
+          <t>5 meningar i ett stycke (737 tecken): Under kursens gång prövar vi hypoteser om språk på grundval av autentiska data och undersöker, genom datorbaserade verkt…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2033</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EN2035</t>
+          <t>EN2034</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (599 tecken): Kursen inleds med en genomgång av den språkvetenskapliga forskningsprocessen, inbegripet ämnesval, problemställning, met…</t>
+          <t>8 meningar i ett stycke (1089 tecken): Denna kurs är en introduktion till centrala typer av språkvetenskaplig dataanalys. Studenterna kommer att lära sig om bå…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EN2037</t>
+          <t>EN2035</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (605 tecken): Kursen innehåller fördjupade studier av olika ämnen inom engelskans sociolingvistik. Vidare undersöks olika faktorer som…</t>
+          <t>4 meningar i ett stycke (599 tecken): Kursen inleds med en genomgång av den språkvetenskapliga forskningsprocessen, inbegripet ämnesval, problemställning, met…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>EN2037</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (808 tecken): Kursen inleds med en genomgång av den språk- eller litteraturvetenskapliga forskningsprocessen, inbegripet ämnesval, pro…</t>
+          <t>4 meningar i ett stycke (605 tecken): Kursen innehåller fördjupade studier av olika ämnen inom engelskans sociolingvistik. Vidare undersöks olika faktorer som…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2037</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EN3062</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1213 tecken): Kursen behandlar världslitteratur på engelska sedan 1960-talet. Den består av fördjupade studier av ett urval representa…</t>
+          <t>5 meningar i ett stycke (808 tecken): Kursen inleds med en genomgång av den språk- eller litteraturvetenskapliga forskningsprocessen, inbegripet ämnesval, pro…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>EN3062</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1154 tecken): Detta andra examensarbete utgör en fördjupning och perspektivisering av det ämnesdidaktiska problemområde som undersökte…</t>
+          <t>8 meningar i ett stycke (1213 tecken): Kursen behandlar världslitteratur på engelska sedan 1960-talet. Den består av fördjupade studier av ett urval representa…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EN3072</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (446 tecken): Vilka fundamentala principer följer vi när vi kommunicerar? Hur skiljer sig tal och skrift åt? På vilka sätt påverkar ol…</t>
+          <t>7 meningar i ett stycke (1154 tecken): Detta andra examensarbete utgör en fördjupning och perspektivisering av det ämnesdidaktiska problemområde som undersökte…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EN3073</t>
+          <t>EN3072</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1129 tecken): Kursen ger en översikt över typiska sätt att analysera språkliga data, med fokus på tillämpad engelsk lingvistik. Studen…</t>
+          <t>5 meningar i ett stycke (446 tecken): Vilka fundamentala principer följer vi när vi kommunicerar? Hur skiljer sig tal och skrift åt? På vilka sätt påverkar ol…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EN3074</t>
+          <t>EN3073</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (797 tecken): Kursen har som syfte att vidareutveckla studentens disciplinspecifika kunskap om och färdigheter i akademiskt skrivande …</t>
+          <t>7 meningar i ett stycke (1129 tecken): Kursen ger en översikt över typiska sätt att analysera språkliga data, med fokus på tillämpad engelsk lingvistik. Studen…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>EN3074</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (998 tecken): Kursen bygger vidare på kursen _Kärnområden inom tillämpad engelsk lingvistik_ och ger en mer fördjupad bild av tillämpa…</t>
+          <t>6 meningar i ett stycke (797 tecken): Kursen har som syfte att vidareutveckla studentens disciplinspecifika kunskap om och färdigheter i akademiskt skrivande …</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (733 tecken): Kursens huvudsakliga innehåll är ett självständigt utfört forskningsprojekt som presenteras i form av en uppsats som omf…</t>
+          <t>4 meningar i ett stycke (998 tecken): Kursen bygger vidare på kursen _Kärnområden inom tillämpad engelsk lingvistik_ och ger en mer fördjupad bild av tillämpa…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GEN2HB</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (700 tecken): Kursen är utformad för att bygga upp affärs-, språk- och kulturella färdigheter. Färdigheterna tränas i praktiska och in…</t>
+          <t>5 meningar i ett stycke (733 tecken): Kursens huvudsakliga innehåll är ett självständigt utfört forskningsprojekt som presenteras i form av en uppsats som omf…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GEN2HB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (924 tecken): Kursen ger en teoretisk grund till språklärande och språkundervisning och kompletterar övriga studier i engelska inför d…</t>
+          <t>5 meningar i ett stycke (700 tecken): Kursen är utformad för att bygga upp affärs-, språk- och kulturella färdigheter. Färdigheterna tränas i praktiska och in…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2HB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1129 tecken): Kursen ger en teoretisk grund till språklärande och språkundervisning och kompletterar övriga studier i engelska inför d…</t>
+          <t>6 meningar i ett stycke (924 tecken): Kursen ger en teoretisk grund till språklärande och språkundervisning och kompletterar övriga studier i engelska inför d…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GEN2RZ</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (909 tecken): Kursen introducerar ett genreperspektiv på muntliga presentationer i akademiska och professionella (arbetslivsrelaterade…</t>
+          <t>7 meningar i ett stycke (1129 tecken): Kursen ger en teoretisk grund till språklärande och språkundervisning och kompletterar övriga studier i engelska inför d…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GEN2S2</t>
+          <t>GEN2RZ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (567 tecken): I kursen får studenterna möjligheter att delta i övningar där de får utforska olika sätt att kommunicera på arbetsplatse…</t>
+          <t>7 meningar i ett stycke (909 tecken): Kursen introducerar ett genreperspektiv på muntliga presentationer i akademiska och professionella (arbetslivsrelaterade…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2S2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GEN2VF</t>
+          <t>GEN2S2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (767 tecken): Kursen består av tre moduler. **Modul 1. Grammatik - 7.5 hp** Grammatikmodulen behandlar grundläggande delar av den enge…</t>
+          <t>4 meningar i ett stycke (567 tecken): I kursen får studenterna möjligheter att delta i övningar där de får utforska olika sätt att kommunicera på arbetsplatse…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2S2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Modulrubrik utan hp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (536 tecken): Kursen innehåller studier av ett urval moderna och samtida barn- och ungdomsverk från den engelskspråkiga världen. Grund…</t>
+          <t>Modulrubrik utan hp-angivelse: 'Modul 1'</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GEN35G</t>
+          <t>GEN2VF</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (464 tecken): Kursen omfattar studier om olika syn på språklärande, som under seminarierna bearbetas och diskuteras. Kursen behandlar …</t>
+          <t>6 meningar i ett stycke (767 tecken): Kursen består av tre moduler. **Modul 1. Grammatik - 7.5 hp** Grammatikmodulen behandlar grundläggande delar av den enge…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VF</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GEN3BQ</t>
+          <t>GEN33R</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (568 tecken): Kursen innehåller ett tematiskt studium av ett antal samtida populära texter från den engelskspråkiga världen. Genom att…</t>
+          <t>5 meningar i ett stycke (536 tecken): Kursen innehåller studier av ett urval moderna och samtida barn- och ungdomsverk från den engelskspråkiga världen. Grund…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GEN3C5</t>
+          <t>GEN35G</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (488 tecken): Kursen består av två moduler. I modulen _Form och funktion_ introduceras perspektiv på skönlitteratur som fokuserar på l…</t>
+          <t>4 meningar i ett stycke (464 tecken): Kursen omfattar studier om olika syn på språklärande, som under seminarierna bearbetas och diskuteras. Kursen behandlar …</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN35G</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GEN3DH</t>
+          <t>GEN3BQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (583 tecken): Kursen introducerar ett urval av representativa litteraturteorier och tillhörande metodologier för litteraturkritik från…</t>
+          <t>4 meningar i ett stycke (568 tecken): Kursen innehåller ett tematiskt studium av ett antal samtida populära texter från den engelskspråkiga världen. Genom att…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BQ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GEN3E6</t>
+          <t>GEN3C5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (703 tecken): Kursen innehåller en översikt av engelsk lingvistik. Kursen behandlar olika perspektiv på språk och betydelse och tillha…</t>
+          <t>5 meningar i ett stycke (488 tecken): Kursen består av två moduler. I modulen _Form och funktion_ introduceras perspektiv på skönlitteratur som fokuserar på l…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GEN3E7</t>
+          <t>GEN3DH</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,51 +1891,51 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (745 tecken): Kursen innehåller ett studium av brittisk och amerikansk litteratur- och idéhistoria från renässansen till postmodernism…</t>
+          <t>4 meningar i ett stycke (583 tecken): Kursen introducerar ett urval av representativa litteraturteorier och tillhörande metodologier för litteraturkritik från…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DH</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1201 tecken): Examensarbetet har en tydlig ämnesdidaktisk prägel och fokuserar på franskämnets vad-, hur- och varför-frågor. Examensar…</t>
+          <t>Osannolikt kort (31 tecken): 'Kursen består av tre delkurser.'</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>GEN3E6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1201 tecken): Examensarbetet har en tydlig ämnesdidaktisk prägel och fokuserar på franskämnets vad-, hur- och varför-frågor. Examensar…</t>
+          <t>5 meningar i ett stycke (703 tecken): Kursen innehåller en översikt av engelsk lingvistik. Kursen behandlar olika perspektiv på språk och betydelse och tillha…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AFR298</t>
+          <t>GEN3E7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (786 tecken): Kursen behandlar franskspråkiga sociala medier ur ett diskursanalytiskt perspektiv. Kursen introducerar begrepp och teor…</t>
+          <t>6 meningar i ett stycke (745 tecken): Kursen innehåller ett studium av brittisk och amerikansk litteratur- och idéhistoria från renässansen till postmodernism…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR298</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AFR29D</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (479 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
+          <t>8 meningar i ett stycke (1201 tecken): Examensarbetet har en tydlig ämnesdidaktisk prägel och fokuserar på franskämnets vad-, hur- och varför-frågor. Examensar…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GFR283</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (401 tecken): Kursen omfattar ett studium av ett urval litterära verk från Maghrebregionen, från 1900- och 2000-talen. Litteraturen be…</t>
+          <t>8 meningar i ett stycke (1201 tecken): Examensarbetet har en tydlig ämnesdidaktisk prägel och fokuserar på franskämnets vad-, hur- och varför-frågor. Examensar…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GFR2HY</t>
+          <t>AFR298</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (440 tecken): Kursen syftar till att vidareutveckla grundläggande kunskaper i franska språket. Den innehåller ett varierat studium av …</t>
+          <t>5 meningar i ett stycke (786 tecken): Kursen behandlar franskspråkiga sociala medier ur ett diskursanalytiskt perspektiv. Kursen introducerar begrepp och teor…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR298</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GFR2HZ</t>
+          <t>AFR29D</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (520 tecken): Kursen syftar till att utveckla grundläggande kunskaper i franska språket och därigenom förbereda den studerande för vid…</t>
+          <t>4 meningar i ett stycke (479 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR29D</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR283</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (476 tecken): Examensarbetet har antingen språk- eller litteraturvetenskaplig inriktning. Inriktning och ämne väljs i samråd med handl…</t>
+          <t>4 meningar i ett stycke (401 tecken): Kursen omfattar ett studium av ett urval litterära verk från Maghrebregionen, från 1900- och 2000-talen. Litteraturen be…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR283</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR2HY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (781 tecken): Kursen utgör en introduktion till språkdidaktik och till de centrala frågor som rör språkundervisningens innehåll och ut…</t>
+          <t>5 meningar i ett stycke (440 tecken): Kursen syftar till att vidareutveckla grundläggande kunskaper i franska språket. Den innehåller ett varierat studium av …</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR2HZ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (936 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
+          <t>5 meningar i ett stycke (520 tecken): Kursen syftar till att utveckla grundläggande kunskaper i franska språket och därigenom förbereda den studerande för vid…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2HZ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GFR3CZ</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (420 tecken): Examensarbetet har språkvetenskaplig, litteraturvetenskaplig eller språkdidaktisk inriktning. Inriktning och ämne väljs …</t>
+          <t>5 meningar i ett stycke (476 tecken): Examensarbetet har antingen språk- eller litteraturvetenskaplig inriktning. Inriktning och ämne väljs i samråd med handl…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GFR3HK</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2220,14 +2220,14 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2247,19 +2247,19 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIT2TE</t>
+          <t>GFR3CZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (424 tecken): I kursen ingår en genomgång av det italienska språkets uttal och fonetiska huvuddrag med tillämpning i praktiska uttalsö…</t>
+          <t>5 meningar i ett stycke (420 tecken): Examensarbetet har språkvetenskaplig, litteraturvetenskaplig eller språkdidaktisk inriktning. Inriktning och ämne väljs …</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AJP23Q</t>
+          <t>GFR3HK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på den euroasiatiska kontinenten. Ett antal centr…</t>
+          <t>5 meningar i ett stycke (781 tecken): Kursen utgör en introduktion till språkdidaktik och till de centrala frågor som rör språkundervisningens innehåll och ut…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AJP23R</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på de amerikanska kontinenterna. Ett antal centra…</t>
+          <t>8 meningar i ett stycke (936 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AJP264</t>
+          <t>GIT2TE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (956 tecken): Kursen fokuserar på jämförande litteraturvetenskaplig analys av migrationstemat ur ett diakront perspektiv. Kursen täcke…</t>
+          <t>4 meningar i ett stycke (424 tecken): I kursen ingår en genomgång av det italienska språkets uttal och fonetiska huvuddrag med tillämpning i praktiska uttalsö…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AJP23Q</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (417 tecken): I kursen läses ett urval av skönlitterära texter på originalspråk. Texterna väljs av den studerande i samråd med läraren…</t>
+          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på den euroasiatiska kontinenten. Ett antal centr…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23Q</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>AJP23R</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (450 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
+          <t>4 meningar i ett stycke (542 tecken): I kursen ges en bred översikt över modern och nutida litteratur skapad på de amerikanska kontinenterna. Ett antal centra…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23R</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AJP2AG</t>
+          <t>AJP264</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (590 tecken): I kursen behandlas både teoretiska aspekter av översättningsvetenskapen och översättningens praktik, med större tonvikt …</t>
+          <t>6 meningar i ett stycke (956 tecken): Kursen fokuserar på jämförande litteraturvetenskaplig analys av migrationstemat ur ett diakront perspektiv. Kursen täcke…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP264</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AJP2AH</t>
+          <t>AJP27A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (994 tecken): Kursen inleds med en översiktlig introduktion till den äldre japanskans stavning och de äldre formerna av skrivtecknen. …</t>
+          <t>4 meningar i ett stycke (417 tecken): I kursen läses ett urval av skönlitterära texter på originalspråk. Texterna väljs av den studerande i samråd med läraren…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GJP2MZ</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (907 tecken): Kursen innehåller övningar i att formulera sig med längre satser och i användandet av ett mer nyansrikt språkbruk. Detta…</t>
+          <t>4 meningar i ett stycke (450 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GJP2N2</t>
+          <t>AJP2AG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (695 tecken): Kursen innehåller övningar i att formulera sig med mer sammansatta meningar och ett mer nyansrikt språk, i synnerhet med…</t>
+          <t>4 meningar i ett stycke (590 tecken): I kursen behandlas både teoretiska aspekter av översättningsvetenskapen och översättningens praktik, med större tonvikt …</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AG</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GJP37V</t>
+          <t>AJP2AH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (506 tecken): Kursen ger en introduktion till olika exempel på grundläggande forskningsmetodik som är vanligt förekommande inom forskn…</t>
+          <t>9 meningar i ett stycke (994 tecken): Kursen inleds med en översiktlig introduktion till den äldre japanskans stavning och de äldre formerna av skrivtecknen. …</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2AH</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GJP37W</t>
+          <t>GJP2MZ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (402 tecken): Kursen ger en översikt över japansk haikupoesi, dess historia och centrala begrepp. Ett stort antal dikter från både äld…</t>
+          <t>8 meningar i ett stycke (907 tecken): Kursen innehåller övningar i att formulera sig med längre satser och i användandet av ett mer nyansrikt språkbruk. Detta…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2MZ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GJP3AY</t>
+          <t>GJP2N2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (541 tecken): Kursen behandlar olika aspekter av japansk manga och anime som en del av den japanska populärkulturen. Efter en kort öve…</t>
+          <t>7 meningar i ett stycke (695 tecken): Kursen innehåller övningar i att formulera sig med mer sammansatta meningar och ett mer nyansrikt språk, i synnerhet med…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP2N2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GJP3B3</t>
+          <t>GJP37V</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (764 tecken): Kursen består av ett individuellt vetenskapligt projekt inom ett ämnesområde relaterat till japansk litteratur, lingvist…</t>
+          <t>5 meningar i ett stycke (506 tecken): Kursen ger en introduktion till olika exempel på grundläggande forskningsmetodik som är vanligt förekommande inom forskn…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37V</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>JP1050</t>
+          <t>GJP37W</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (635 tecken): Med hjälp av praktiska skriv- och läsövningar, övar studenterna upp förmågan att använda de fonetiska skriftsystemen. Dä…</t>
+          <t>4 meningar i ett stycke (402 tecken): Kursen ger en översikt över japansk haikupoesi, dess historia och centrala begrepp. Ett stort antal dikter från både äld…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP37W</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AKI2BN</t>
+          <t>GJP3AY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (627 tecken): Kursen integrerar avancerad språkfärdighetsträning med teoretiska verktyg för att analysera och diskutera centrala samhä…</t>
+          <t>4 meningar i ett stycke (541 tecken): Kursen behandlar olika aspekter av japansk manga och anime som en del av den japanska populärkulturen. Efter en kort öve…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3AY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GKI27H</t>
+          <t>GJP3B3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (593 tecken): Kursen omfattar sex moduler som bygger på varandra. De separata språkmomenten som att lyssna, tala, läsa och skriva inte…</t>
+          <t>7 meningar i ett stycke (764 tecken): Kursen består av ett individuellt vetenskapligt projekt inom ett ämnesområde relaterat till japansk litteratur, lingvist…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>JP1050</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (480 tecken): Kursen består av två moduler: 1. Tala och lyssna: I den här modulen tränar studenten på att tala och lyssna genom gramma…</t>
+          <t>4 meningar i ett stycke (635 tecken): Med hjälp av praktiska skriv- och läsövningar, övar studenterna upp förmågan att använda de fonetiska skriftsystemen. Dä…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1050</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GKI2QA</t>
+          <t>AKI2BN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (538 tecken): Kursen består av ett individuellt projekt inom något av ämnesområdena kinesisk litteratur, lingvistik, kulturella studie…</t>
+          <t>4 meningar i ett stycke (627 tecken): Kursen integrerar avancerad språkfärdighetsträning med teoretiska verktyg för att analysera och diskutera centrala samhä…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GKI2VM</t>
+          <t>GKI27H</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (535 tecken): I kursen studeras inlärning av och undervisning i kinesiska som främmande språk i ljuset av aktuell forskning. Didaktisk…</t>
+          <t>6 meningar i ett stycke (593 tecken): Kursen omfattar sex moduler som bygger på varandra. De separata språkmomenten som att lyssna, tala, läsa och skriva inte…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27H</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GKI3CA</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (549 tecken): Kursen omfattar sex delmoment som bygger på varandra. De fyra färdigheterna lyssna, tala, läsa och skriva integreras i m…</t>
+          <t>4 meningar i ett stycke (480 tecken): Kursen består av två moduler: 1. Tala och lyssna: I den här modulen tränar studenten på att tala och lyssna genom gramma…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GKI3CB</t>
+          <t>GKI2QA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (506 tecken): Kursen omfattar sex delmoment som bygger på varandra. De fyra färdigheterna lyssna, tala, läsa och skriva integreras i m…</t>
+          <t>5 meningar i ett stycke (538 tecken): Kursen består av ett individuellt projekt inom något av ämnesområdena kinesisk litteratur, lingvistik, kulturella studie…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2QA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GKI3CD</t>
+          <t>GKI2VM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (538 tecken): Kursen består av ett individuellt projekt inom något av ämnesområdena kinesisk litteratur, lingvistik, kulturella studie…</t>
+          <t>4 meningar i ett stycke (535 tecken): I kursen studeras inlärning av och undervisning i kinesiska som främmande språk i ljuset av aktuell forskning. Didaktisk…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2VM</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GKI3GQ</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (577 tecken): Kursen introducerar kinesisk litteratur och litteraturteorier, med fokus på närläsning av texter från den sena Qingdynas…</t>
+          <t>Osannolikt kort (46 tecken): 'Kursen består av fyra obligatoriska delkurser:'</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KI1046</t>
+          <t>GKI3CA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (815 tecken): Kursen omfattar sex delmoment, som bygger på varandra. De separata språkmomenten som att lyssna, tala, läsa och skriva i…</t>
+          <t>4 meningar i ett stycke (549 tecken): Kursen omfattar sex delmoment som bygger på varandra. De fyra färdigheterna lyssna, tala, läsa och skriva integreras i m…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CA</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KI2001</t>
+          <t>GKI3CB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (642 tecken): Kursen erbjuder en översiktlig introduktion till den kinesiska 1900-talslitteraturen genom utvalda representativa, och l…</t>
+          <t>4 meningar i ett stycke (506 tecken): Kursen omfattar sex delmoment som bygger på varandra. De fyra färdigheterna lyssna, tala, läsa och skriva integreras i m…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CB</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>KI2012</t>
+          <t>GKI3CD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (441 tecken): I kursen studeras olika exempel på grundläggande forskningsmetodik som är vanligt förekommande inom forskning om kinesis…</t>
+          <t>5 meningar i ett stycke (538 tecken): Kursen består av ett individuellt projekt inom något av ämnesområdena kinesisk litteratur, lingvistik, kulturella studie…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CD</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GPR256</t>
+          <t>GKI3GQ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (913 tecken): Inom kursens ram författas en vetenskaplig studie på portugisiska, engelska eller svenska, om c:a 6000 - 10 000 ord utif…</t>
+          <t>4 meningar i ett stycke (577 tecken): Kursen introducerar kinesisk litteratur och litteraturteorier, med fokus på närläsning av texter från den sena Qingdynas…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3GQ</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GPR2W2</t>
+          <t>KI1046</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (653 tecken): I kursen studeras olika perspektiv inom modern språkforskning med utgångspunkt i konkreta studier från portugisiskspråki…</t>
+          <t>7 meningar i ett stycke (815 tecken): Kursen omfattar sex delmoment, som bygger på varandra. De separata språkmomenten som att lyssna, tala, läsa och skriva i…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1046</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GPR2X9</t>
+          <t>KI2001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (689 tecken): Kursen innehåller studier av skönlitterära texter, filmatiseringar, sakprosa och annat samtidsmaterial som belyser Portu…</t>
+          <t>5 meningar i ett stycke (642 tecken): Kursen erbjuder en översiktlig introduktion till den kinesiska 1900-talslitteraturen genom utvalda representativa, och l…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2001</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GPR2XS</t>
+          <t>KI2012</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (462 tecken): Kursen innehåller grundläggande studier i allmän och portugisisk fonetik och uttal. Skillnader mellan olika språkvariete…</t>
+          <t>4 meningar i ett stycke (441 tecken): I kursen studeras olika exempel på grundläggande forskningsmetodik som är vanligt förekommande inom forskning om kinesis…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI2012</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GPR2Z2</t>
+          <t>GPR256</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (567 tecken): I kursen studeras och analyseras olika exempel på vetenskapliga studier inom litteratur-, kultur- och språkvetenskap. Ut…</t>
+          <t>7 meningar i ett stycke (913 tecken): Inom kursens ram författas en vetenskaplig studie på portugisiska, engelska eller svenska, om c:a 6000 - 10 000 ord utif…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2Z2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GPR3E5</t>
+          <t>GPR2W2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1082 tecken): Kursen består av tre delar, _Introduktion_, _Praktik _och _Teoretiska perspektiv_. I introduktionsdelen deltar studenter…</t>
+          <t>5 meningar i ett stycke (653 tecken): I kursen studeras olika perspektiv inom modern språkforskning med utgångspunkt i konkreta studier från portugisiskspråki…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2W2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GPR3GR</t>
+          <t>GPR2X9</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1082 tecken): Kursen består av tre delar, _Introduktion_, _Praktik _och _Teoretiska perspektiv_. I introduktionsdelen deltar studenter…</t>
+          <t>4 meningar i ett stycke (689 tecken): Kursen innehåller studier av skönlitterära texter, filmatiseringar, sakprosa och annat samtidsmaterial som belyser Portu…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2X9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>PR1019</t>
+          <t>GPR2XS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (839 tecken): Kursen är en fortsättning på Grundläggande kurs I och fokuserar på grundläggande språkfärdigheter som motsvarar nivå A2 …</t>
+          <t>4 meningar i ett stycke (462 tecken): Kursen innehåller grundläggande studier i allmän och portugisisk fonetik och uttal. Skillnader mellan olika språkvariete…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>PR1024</t>
+          <t>GPR2Z2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (571 tecken): Kursen bygger vidare på kursen _Portugisisk grammatik och skriftlig språkfärdighet I_ och omfattar en fördjupning i stud…</t>
+          <t>5 meningar i ett stycke (567 tecken): I kursen studeras och analyseras olika exempel på vetenskapliga studier inom litteratur-, kultur- och språkvetenskap. Ut…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2Z2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>PR2003</t>
+          <t>GPR3E5</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (799 tecken): Kursen innehåller två centrala delar. I den ena delen beskrivs geografisk variation i portugisiska i världen och i denna…</t>
+          <t>9 meningar i ett stycke (1082 tecken): Kursen består av tre delar, _Introduktion_, _Praktik _och _Teoretiska perspektiv_. I introduktionsdelen deltar studenter…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3E5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PR2005</t>
+          <t>GPR3GR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (717 tecken): I kursen studeras olika exempel på portugisiskspråkiga vetenskapliga studier inom litteratur- och språkvetenskap. Utifrå…</t>
+          <t>9 meningar i ett stycke (1082 tecken): Kursen består av tre delar, _Introduktion_, _Praktik _och _Teoretiska perspektiv_. I introduktionsdelen deltar studenter…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GR</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ARY23F</t>
+          <t>PR1019</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (640 tecken): Kursen fokuserar på det sovjetiska experimentet att skapa en ny kulturformation, ”den sovjetiska socialistiska kulturen”…</t>
+          <t>5 meningar i ett stycke (839 tecken): Kursen är en fortsättning på Grundläggande kurs I och fokuserar på grundläggande språkfärdigheter som motsvarar nivå A2 …</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1019</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GRY287</t>
+          <t>PR1024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (468 tecken): Under kursens gång utvecklar den studerande förmågan att utföra syntaktisk analys av valda ryska texter utifrån ett teor…</t>
+          <t>4 meningar i ett stycke (571 tecken): Kursen bygger vidare på kursen _Portugisisk grammatik och skriftlig språkfärdighet I_ och omfattar en fördjupning i stud…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY287</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1024</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GRY28P</t>
+          <t>PR2003</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (715 tecken): Kursen behandlar det ryska språkets framväxt i relation till andra slaviska samt indoeuropeiska språk. Inom kursen disku…</t>
+          <t>7 meningar i ett stycke (799 tecken): Kursen innehåller två centrala delar. I den ena delen beskrivs geografisk variation i portugisiska i världen och i denna…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2003</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GRY28U</t>
+          <t>PR2005</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (511 tecken): Kursen ger en introduktion till centrala litterära verk från 1800-talet fram till 1917. Därtill belyser kursen litteratu…</t>
+          <t>5 meningar i ett stycke (717 tecken): I kursen studeras olika exempel på portugisiskspråkiga vetenskapliga studier inom litteratur- och språkvetenskap. Utifrå…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR2005</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GRY2B4</t>
+          <t>ARY23F</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (577 tecken): Kursen ger en introduktion till den ryska litteraturen från 1917 och fram till 1991. Under kursens gång studeras betydel…</t>
+          <t>4 meningar i ett stycke (640 tecken): Kursen fokuserar på det sovjetiska experimentet att skapa en ny kulturformation, ”den sovjetiska socialistiska kulturen”…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARY23F</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GRY2BR</t>
+          <t>GRY287</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (639 tecken): Kursen fokuserar på transformationen av den ryska kulturen och litteraturen från 1991 till idag. Övergången från det sen…</t>
+          <t>4 meningar i ett stycke (468 tecken): Under kursens gång utvecklar den studerande förmågan att utföra syntaktisk analys av valda ryska texter utifrån ett teor…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY287</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>GRY28P</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (692 tecken): Kursen behandlar den ryska operan under 1800-talet och fram till 1917 såsom den ledande genren inom rysk musik och en av…</t>
+          <t>5 meningar i ett stycke (715 tecken): Kursen behandlar det ryska språkets framväxt i relation till andra slaviska samt indoeuropeiska språk. Inom kursen disku…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28P</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GRY2LE</t>
+          <t>GRY28U</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (519 tecken): Kursen behandlar rysk folklore, dess viktigaste genrer, karaktärer och motiv samt deras utveckling över tid. Ett urval t…</t>
+          <t>5 meningar i ett stycke (511 tecken): Kursen ger en introduktion till centrala litterära verk från 1800-talet fram till 1917. Därtill belyser kursen litteratu…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY28U</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GRY2YW</t>
+          <t>GRY2B4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (604 tecken): Kursen behandlar centrala språkutvecklingsteorier som under seminarierna belyses och diskuteras ur olika perspektiv. Där…</t>
+          <t>5 meningar i ett stycke (577 tecken): Kursen ger en introduktion till den ryska litteraturen från 1917 och fram till 1991. Under kursens gång studeras betydel…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2B4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GRY2BR</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (671 tecken): Kursen behandlar den ryska operans utveckling från 1917 och fram till efterkrigstiden såsom en av de viktigaste konstart…</t>
+          <t>6 meningar i ett stycke (639 tecken): Kursen fokuserar på transformationen av den ryska kulturen och litteraturen från 1991 till idag. Övergången från det sen…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BR</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GRY36F</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (429 tecken): I kursen studeras ett urval filmatiseringar av ryska skönlitterära verk från 1800- och 1900-talet. Därtill diskuteras fi…</t>
+          <t>5 meningar i ett stycke (692 tecken): Kursen behandlar den ryska operan under 1800-talet och fram till 1917 såsom den ledande genren inom rysk musik och en av…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GRY2LE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (732 tecken): Kursen behandlar betydelsefulla verk i rysk film från 1900-talets början till och med nu i relation till samhälleliga fö…</t>
+          <t>5 meningar i ett stycke (519 tecken): Kursen behandlar rysk folklore, dess viktigaste genrer, karaktärer och motiv samt deras utveckling över tid. Ett urval t…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2LE</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GRY2YW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (496 tecken): Kursen behandlar ett urval av sovjetiska och postsovjetiska science fiction-filmer. I kursen belyses och diskuteras scie…</t>
+          <t>4 meningar i ett stycke (604 tecken): Kursen behandlar centrala språkutvecklingsteorier som under seminarierna belyses och diskuteras ur olika perspektiv. Där…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1068 tecken): I kursen utförs ett examensarbete med en tydlig ämnesdidaktisk prägel som fokuserar på spanskämnets vad-, hur- och varfö…</t>
+          <t>5 meningar i ett stycke (671 tecken): Kursen behandlar den ryska operans utveckling från 1917 och fram till efterkrigstiden såsom en av de viktigaste konstart…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GRY36F</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1068 tecken): I kursen utförs ett examensarbete med en tydlig ämnesdidaktisk prägel som fokuserar på spanskämnets vad-, hur- och varfö…</t>
+          <t>4 meningar i ett stycke (429 tecken): I kursen studeras ett urval filmatiseringar av ryska skönlitterära verk från 1800- och 1900-talet. Därtill diskuteras fi…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (908 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
+          <t>4 meningar i ett stycke (732 tecken): Kursen behandlar betydelsefulla verk i rysk film från 1900-talets början till och med nu i relation till samhälleliga fö…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSP2SK</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (477 tecken): Kursen omfattar en bred översikt av spansk och spanskamerikansk historia och samhällsliv. I undervisningen används sakpr…</t>
+          <t>4 meningar i ett stycke (496 tecken): Kursen behandlar ett urval av sovjetiska och postsovjetiska science fiction-filmer. I kursen belyses och diskuteras scie…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSP2SL</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (500 tecken): Kursen omfattar en genomgång av spanskans stavnings- och betoningsregler och grundläggande fonetiska och fonologiska dra…</t>
+          <t>7 meningar i ett stycke (1068 tecken): I kursen utförs ett examensarbete med en tydlig ämnesdidaktisk prägel som fokuserar på spanskämnets vad-, hur- och varfö…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSP2W6</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (781 tecken): Kursen utgör en introduktion till språkdidaktik och till de centrala frågor som rör språkundervisningens innehåll och ut…</t>
+          <t>7 meningar i ett stycke (1068 tecken): I kursen utförs ett examensarbete med en tydlig ämnesdidaktisk prägel som fokuserar på spanskämnets vad-, hur- och varfö…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (433 tecken): Den studerande reflekterar kring olika språkvetenskapliga eller litteraturvetenskapliga metoder. Under kursens gång övar…</t>
+          <t>7 meningar i ett stycke (908 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSP39N</t>
+          <t>GSP2SK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (469 tecken): Kursen syftar till att utveckla grundläggande kunskaper i spanska språket och därigenom förbereda den studerande för vid…</t>
+          <t>4 meningar i ett stycke (477 tecken): Kursen omfattar en bred översikt av spansk och spanskamerikansk historia och samhällsliv. I undervisningen används sakpr…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>SP1050</t>
+          <t>GSP2SL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (612 tecken): Kursen omfattar en fördjupning av den grammatik som studerades på Spanska I. Stort fokus läggs på den studerandes medvet…</t>
+          <t>4 meningar i ett stycke (500 tecken): Kursen omfattar en genomgång av spanskans stavnings- och betoningsregler och grundläggande fonetiska och fonologiska dra…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SL</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP2W6</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (695 tecken): Kursen omfattar studier av den moderna lingvistikens grundbegrepp och terminologi och syftar till att förmedla ökad förs…</t>
+          <t>5 meningar i ett stycke (781 tecken): Kursen utgör en introduktion till språkdidaktik och till de centrala frågor som rör språkundervisningens innehåll och ut…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (589 tecken): Kursen behandlar ett urval skönlitterära verk och filmer som representerar olika perioder i Spaniens litteratur och kult…</t>
+          <t>4 meningar i ett stycke (433 tecken): Den studerande reflekterar kring olika språkvetenskapliga eller litteraturvetenskapliga metoder. Under kursens gång övar…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>GSP39N</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (601 tecken): Kursen behandlar ett urval skönlitterära verk och film som representerar olika perioder i Latinamerikas litteratur och k…</t>
+          <t>4 meningar i ett stycke (469 tecken): Kursen syftar till att utveckla grundläggande kunskaper i spanska språket och därigenom förbereda den studerande för vid…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP39N</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>SP1050</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3970,19 +3970,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (735 tecken): Kursen inleds med en genomgång av den litteraturvetenskapliga forskningsprocessen, inbegripet ämnesval, problemställning…</t>
+          <t>5 meningar i ett stycke (612 tecken): Kursen omfattar en fördjupning av den grammatik som studerades på Spanska I. Stort fokus läggs på den studerandes medvet…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1050</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (563 tecken): Kursen fokuserar på 1900-talets viktigaste litterära uttryck i Spanien och Spanskamerika. Huvudstudieobjektet utgörs av …</t>
+          <t>4 meningar i ett stycke (695 tecken): Kursen omfattar studier av den moderna lingvistikens grundbegrepp och terminologi och syftar till att förmedla ökad förs…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4024,19 +4024,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (418 tecken): Kursen fokuserar på den spanska litteraturen från guldåldern till realismen. Tonvikten läggs vid litterär analys med ank…</t>
+          <t>4 meningar i ett stycke (589 tecken): Kursen behandlar ett urval skönlitterära verk och filmer som representerar olika perioder i Spaniens litteratur och kult…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SP1053</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1218 tecken): Kursen introducerar de teoretiska grunderna för sociolingvistiska variationer i olika spansktalande samhällen. Vidare be…</t>
+          <t>4 meningar i ett stycke (601 tecken): Kursen behandlar ett urval skönlitterära verk och film som representerar olika perioder i Latinamerikas litteratur och k…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (822 tecken): Denna kurs ger fördjupade kunskaper om nationella minoritetsspråk med särskilt fokus på Sveriges nationella minoriteters…</t>
+          <t>5 meningar i ett stycke (735 tecken): Kursen inleds med en genomgång av den litteraturvetenskapliga forskningsprocessen, inbegripet ämnesval, problemställning…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (735 tecken): I kursen belyses betydelsen av studiehandledning på modersmål för nyanlända och flerspråkiga elevers språk- och kunskaps…</t>
+          <t>5 meningar i ett stycke (563 tecken): Kursen fokuserar på 1900-talets viktigaste litterära uttryck i Spanien och Spanskamerika. Huvudstudieobjektet utgörs av …</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,24 +4132,24 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (977 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar andraspråkselevers och nyanlända elevers l…</t>
+          <t>4 meningar i ett stycke (418 tecken): Kursen fokuserar på den spanska litteraturen från guldåldern till realismen. Tonvikten läggs vid litterär analys med ank…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSS2BY</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4159,19 +4159,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (482 tecken): I kursen behandlas det svenska språkets struktur i ett språktypologiskt och tvärspråkligt perspektiv främst vad gäller m…</t>
+          <t>9 meningar i ett stycke (1218 tecken): Kursen introducerar de teoretiska grunderna för sociolingvistiska variationer i olika spansktalande samhällen. Vidare be…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSS2BZ</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (764 tecken): I denna kurs behandlas skriftspråksutveckling i första hand på ett andraspråk. Skriftspråksutveckling på svenska belyses…</t>
+          <t>5 meningar i ett stycke (822 tecken): Denna kurs ger fördjupade kunskaper om nationella minoritetsspråk med särskilt fokus på Sveriges nationella minoriteters…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSS2C4</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4213,19 +4213,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (546 tecken): Kursen behandlar bedömning av inlärares språkfärdighet ur olika perspektiv och utifrån olika bedömningsmodeller. Bedömni…</t>
+          <t>5 meningar i ett stycke (735 tecken): I kursen belyses betydelsen av studiehandledning på modersmål för nyanlända och flerspråkiga elevers språk- och kunskaps…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSS2C5</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (519 tecken): I kursen behandlas det svenska språkets fonetik och fonologi ur ett andraspråksperspektiv. Särskild tyngdpunkt läggs på …</t>
+          <t>5 meningar i ett stycke (977 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar andraspråkselevers och nyanlända elevers l…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSS2FJ</t>
+          <t>GSS2BY</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4267,19 +4267,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (615 tecken): Denna kurs behandlar flerspråkighet som fenomen samt villkor för utveckling av ett andraspråk. Inom kursens ram diskuter…</t>
+          <t>5 meningar i ett stycke (482 tecken): I kursen behandlas det svenska språkets struktur i ett språktypologiskt och tvärspråkligt perspektiv främst vad gäller m…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSS36C</t>
+          <t>GSS2BZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (604 tecken): I kursen behandlas sociolingvistiska perspektiv på flerspråkighet med ett särskilt fokus på interaktion och olika språkl…</t>
+          <t>8 meningar i ett stycke (764 tecken): I denna kurs behandlas skriftspråksutveckling i första hand på ett andraspråk. Skriftspråksutveckling på svenska belyses…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSS2C4</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,19 +4321,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (956 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar andraspråkselevers och nyanlända elevers l…</t>
+          <t>5 meningar i ett stycke (546 tecken): Kursen behandlar bedömning av inlärares språkfärdighet ur olika perspektiv och utifrån olika bedömningsmodeller. Bedömni…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSS2C5</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (950 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar andraspråkselevers och ungdomars lärande, …</t>
+          <t>4 meningar i ett stycke (519 tecken): I kursen behandlas det svenska språkets fonetik och fonologi ur ett andraspråksperspektiv. Särskild tyngdpunkt läggs på …</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS2FJ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4375,19 +4375,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (967 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar vuxna andraspråkselevers lärande, identite…</t>
+          <t>5 meningar i ett stycke (615 tecken): Denna kurs behandlar flerspråkighet som fenomen samt villkor för utveckling av ett andraspråk. Inom kursens ram diskuter…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS3BG</t>
+          <t>GSS36C</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4402,19 +4402,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (496 tecken): Kursen har en kommunikativ och en till viss del språkvetenskaplig inriktning. Kursen ger en överblick över svenskans gru…</t>
+          <t>6 meningar i ett stycke (604 tecken): I kursen behandlas sociolingvistiska perspektiv på flerspråkighet med ett särskilt fokus på interaktion och olika språkl…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSS3BH</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4429,19 +4429,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (573 tecken): Kursen behandlar svenska språkets grundläggande struktur och har en kommunikativ och viss språkvetenskaplig inriktning. …</t>
+          <t>5 meningar i ett stycke (956 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar andraspråkselevers och nyanlända elevers l…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSS3BJ</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4456,19 +4456,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (601 tecken): Kursen har en kommunikativ och viss språkvetenskaplig inriktning. Under kursen sker ett fördjupat arbete med svenska spr…</t>
+          <t>5 meningar i ett stycke (950 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar andraspråkselevers och ungdomars lärande, …</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GSS3BK</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4483,19 +4483,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (569 tecken): Kursen har en kommunikativ och viss språkvetenskaplig inriktning. Under kursen sker ett fördjupat arbete med svenska spr…</t>
+          <t>5 meningar i ett stycke (967 tecken): I denna kurs behandlas faktorer på samhälls- och utbildningsnivå som påverkar vuxna andraspråkselevers lärande, identite…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSS3BM</t>
+          <t>GSS3BG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (843 tecken): I denna kurs behandlas centrala didaktiska teorier om hur andraspråksutveckling kan stödjas genom undervisning samt olik…</t>
+          <t>5 meningar i ett stycke (496 tecken): Kursen har en kommunikativ och en till viss del språkvetenskaplig inriktning. Kursen ger en överblick över svenskans gru…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BG</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSS3BH</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (477 tecken): I denna kurs behandlas lärande genom fiktionstext i andraspråksundervisningen. Metoder och modeller för att analysera fi…</t>
+          <t>4 meningar i ett stycke (573 tecken): Kursen behandlar svenska språkets grundläggande struktur och har en kommunikativ och viss språkvetenskaplig inriktning. …</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BH</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GSS3H9</t>
+          <t>GSS3BJ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,19 +4564,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (741 tecken): I kursen fördjupas diskussionen om relationer mellan utveckling av språk och kunskap i skolans olika ämnen. Dessutom för…</t>
+          <t>5 meningar i ett stycke (601 tecken): Kursen har en kommunikativ och viss språkvetenskaplig inriktning. Under kursen sker ett fördjupat arbete med svenska spr…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BJ</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GSS3HC</t>
+          <t>GSS3BK</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (593 tecken): I kursen behandlas styrdokument och stödmaterial med fokus på modersmålsundervisning och studiehandledning. I kursen beh…</t>
+          <t>6 meningar i ett stycke (569 tecken): Kursen har en kommunikativ och viss språkvetenskaplig inriktning. Under kursen sker ett fördjupat arbete med svenska spr…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BK</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSS3HD</t>
+          <t>GSS3BM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,19 +4618,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (737 tecken): I kursen behandlas teorier om språk- och kunskapsutveckling och forskning med fokus på flerspråkighet och modersmål. Vid…</t>
+          <t>5 meningar i ett stycke (843 tecken): I denna kurs behandlas centrala didaktiska teorier om hur andraspråksutveckling kan stödjas genom undervisning samt olik…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (710 tecken): I denna kurs behandlas sociolingvistiska perspektiv på modersmålsundervisning med fokus på relationen mellan språk, inte…</t>
+          <t>4 meningar i ett stycke (477 tecken): I denna kurs behandlas lärande genom fiktionstext i andraspråksundervisningen. Metoder och modeller för att analysera fi…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>GSS3H9</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (555 tecken): I denna kurs fokuseras skriftspråksutveckling ur ett flerspråkigt perspektiv och skriftspråkets betydelse för lärande in…</t>
+          <t>6 meningar i ett stycke (741 tecken): I kursen fördjupas diskussionen om relationer mellan utveckling av språk och kunskap i skolans olika ämnen. Dessutom för…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSS3HH</t>
+          <t>GSS3HC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4699,19 +4699,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (529 tecken): I denna kurs behandlas lärande genom fiktionstext i andraspråksundervisningen. De litterära perioderna, verkens centrala…</t>
+          <t>5 meningar i ett stycke (593 tecken): I kursen behandlas styrdokument och stödmaterial med fokus på modersmålsundervisning och studiehandledning. I kursen beh…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS3HD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (876 tecken): I kursen behandlas skönlitteraturens betydelse i undervisningen i skolämnet svenska som andraspråk på gymnasial nivå. Ol…</t>
+          <t>5 meningar i ett stycke (737 tecken): I kursen behandlas teorier om språk- och kunskapsutveckling och forskning med fokus på flerspråkighet och modersmål. Vid…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SS3002</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4753,19 +4753,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (825 tecken): I denna kurs behandlas teoretiska och metodologiska frågor samt aktuella forskningsresultat relaterade till flerspråkigh…</t>
+          <t>4 meningar i ett stycke (710 tecken): I denna kurs behandlas sociolingvistiska perspektiv på modersmålsundervisning med fokus på relationen mellan språk, inte…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SS3003</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4780,19 +4780,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (902 tecken): I denna kurs behandlas teoretiska och metodologiska frågor samt aktuella forskningsresultat relaterade till studium av s…</t>
+          <t>5 meningar i ett stycke (555 tecken): I denna kurs fokuseras skriftspråksutveckling ur ett flerspråkigt perspektiv och skriftspråkets betydelse för lärande in…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>GSS3HH</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (679 tecken): I denna kurs behandlas svenska språket som ett andraspråk ur ett tvärspråkligt perspektiv. Frågor relaterade till språkt…</t>
+          <t>5 meningar i ett stycke (529 tecken): I denna kurs behandlas lärande genom fiktionstext i andraspråksundervisningen. De litterära perioderna, verkens centrala…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SS3006</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (960 tecken): Kursen belyser relationer mellan migrationsprocesser, kulturmöten och identitetsprocesser i ett flerspråkigt perspektiv.…</t>
+          <t>6 meningar i ett stycke (876 tecken): I kursen behandlas skönlitteraturens betydelse i undervisningen i skolämnet svenska som andraspråk på gymnasial nivå. Ol…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3002</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4861,19 +4861,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (856 tecken): _ _I kursen behandlas aktuell forskning kring flerspråkighet i klassrummet där särskilt betydelsen av interaktion för sp…</t>
+          <t>5 meningar i ett stycke (825 tecken): I denna kurs behandlas teoretiska och metodologiska frågor samt aktuella forskningsresultat relaterade till flerspråkigh…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>SS3008</t>
+          <t>SS3003</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (621 tecken): I denna kurs utvecklar den studerande fördjupade kunskaper om svenskspråkig skönlitteratur med flerspråkiga röster. Skön…</t>
+          <t>7 meningar i ett stycke (902 tecken): I denna kurs behandlas teoretiska och metodologiska frågor samt aktuella forskningsresultat relaterade till studium av s…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4915,19 +4915,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (605 tecken): I denna kurs studeras litteracitet utifrån ett flerspråkigt perspektiv. Den teoretiska ansatsen är etnolingvistisk, vilk…</t>
+          <t>6 meningar i ett stycke (679 tecken): I denna kurs behandlas svenska språket som ett andraspråk ur ett tvärspråkligt perspektiv. Frågor relaterade till språkt…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>SS3006</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,19 +4942,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (404 tecken): I kursen belyses olika aspekter av andraspråksuttal. De fonologiska och artikulatorisk-akustiska dragen tas upp till ana…</t>
+          <t>6 meningar i ett stycke (960 tecken): Kursen belyser relationer mellan migrationsprocesser, kulturmöten och identitetsprocesser i ett flerspråkigt perspektiv.…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (642 tecken): Inom denna kurs fördjupar sig studenten inom något område inom andraspråksfältet genom att självständigt planera och gen…</t>
+          <t>7 meningar i ett stycke (856 tecken): _ _I kursen behandlas aktuell forskning kring flerspråkighet i klassrummet där särskilt betydelsen av interaktion för sp…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>SS3008</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (779 tecken): I denna kurs behandlas flerspråkighet i ett samhällsperspektiv med betoning på språkpolitik, språkplanering och språkide…</t>
+          <t>4 meningar i ett stycke (621 tecken): I denna kurs utvecklar den studerande fördjupade kunskaper om svenskspråkig skönlitteratur med flerspråkiga röster. Skön…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GSV2P9</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (779 tecken): I kursen behandlas teoretiska och didaktiska perspektiv på språkutveckling med fokus på läs- och skrivinlärning, läsutve…</t>
+          <t>5 meningar i ett stycke (605 tecken): I denna kurs studeras litteracitet utifrån ett flerspråkigt perspektiv. Den teoretiska ansatsen är etnolingvistisk, vilk…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1230 tecken): I kursen behandlas didaktiska och metodikinriktade perspektiv på elevers läs- och skrivutveckling, där ”The Simple View …</t>
+          <t>4 meningar i ett stycke (404 tecken): I kursen belyses olika aspekter av andraspråksuttal. De fonologiska och artikulatorisk-akustiska dragen tas upp till ana…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1073 tecken): I kursen behandlas teoretiska och didaktiska perspektiv på språkutveckling med fokus på grundläggande läs- och skrivinlä…</t>
+          <t>5 meningar i ett stycke (642 tecken): Inom denna kurs fördjupar sig studenten inom något område inom andraspråksfältet genom att självständigt planera och gen…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1187 tecken): I kursen genomförs ett vetenskapligt arbete som har en tydlig ämnesdidaktisk prägel. Det är dels en fördjupning av de äm…</t>
+          <t>6 meningar i ett stycke (779 tecken): I denna kurs behandlas flerspråkighet i ett samhällsperspektiv med betoning på språkpolitik, språkplanering och språkide…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>GSV2P9</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1203 tecken): I kursen genomförs ett omfattande vetenskapligt arbete som har en tydlig ämnesdidaktisk prägel. Det är dels en fördjupni…</t>
+          <t>6 meningar i ett stycke (779 tecken): I kursen behandlas teoretiska och didaktiska perspektiv på språkutveckling med fokus på läs- och skrivinlärning, läsutve…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ATY29E</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5158,24 +5158,24 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (476 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
+          <t>8 meningar i ett stycke (1230 tecken): I kursen behandlas didaktiska och metodikinriktade perspektiv på elevers läs- och skrivutveckling, där ”The Simple View …</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (744 tecken): I kursen utforskas interaktionen i digitala medier och med AI-baserade verktyg, med särskilt fokus på hur språkanvändarn…</t>
+          <t>7 meningar i ett stycke (1073 tecken): I kursen behandlas teoretiska och didaktiska perspektiv på språkutveckling med fokus på grundläggande läs- och skrivinlä…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (561 tecken): I kursen studeras ett urval texter från nutida tyskspråkig barn- och ungdomsfiktion. Kursen utgår från ett brett littera…</t>
+          <t>8 meningar i ett stycke (1187 tecken): I kursen genomförs ett vetenskapligt arbete som har en tydlig ämnesdidaktisk prägel. Det är dels en fördjupning av de äm…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GTY2SV</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (801 tecken): Kursen fokuserar på den didaktiska tillämpningen av tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida skönl…</t>
+          <t>8 meningar i ett stycke (1203 tecken): I kursen genomförs ett omfattande vetenskapligt arbete som har en tydlig ämnesdidaktisk prägel. Det är dels en fördjupni…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GTY2SZ</t>
+          <t>ATY29E</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (570 tecken): Kursen innehåller övningar i att förstå tyskt tal och i att kommunicera på tyska i olika situationer och inom olika ämne…</t>
+          <t>4 meningar i ett stycke (476 tecken): I kursen genomförs en självständigt författad litteraturvetenskaplig studie inom ett avgränsat problemområde med relevan…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY29E</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (936 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
+          <t>5 meningar i ett stycke (744 tecken): I kursen utforskas interaktionen i digitala medier och med AI-baserade verktyg, med särskilt fokus på hur språkanvändarn…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GTY369</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (664 tecken): Kursen innehåller en genomgång av elementär fonetik samt av principerna för tyskt uttal. Den innehåller övningar i att f…</t>
+          <t>4 meningar i ett stycke (561 tecken): I kursen studeras ett urval texter från nutida tyskspråkig barn- och ungdomsfiktion. Kursen utgår från ett brett littera…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GTY3J5</t>
+          <t>GTY2SV</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (630 tecken): Kursen omfattar dels ett fördjupat studium av tysk formlära och syntax med fokus på kontrastivt viktiga skillnader mella…</t>
+          <t>6 meningar i ett stycke (801 tecken): Kursen fokuserar på den didaktiska tillämpningen av tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida skönl…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SV</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GTY3J7</t>
+          <t>GTY2SZ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (720 tecken): Inom modulen _Muntlig språkfärdighet_ läggs stor vikt vid att träna den egna språkliga kompetensen med ett brett ordförr…</t>
+          <t>4 meningar i ett stycke (570 tecken): Kursen innehåller övningar i att förstå tyskt tal och i att kommunicera på tyska i olika situationer och inom olika ämne…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GTY3J8</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (624 tecken): I kursen studeras dels den tyskspråkiga barn- och ungdomslitteraturens historiska utveckling, dels ett urval texter från…</t>
+          <t>8 meningar i ett stycke (936 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GTY369</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (904 tecken): Kursen utgör en introduktion till språkdidaktiken och till de centrala frågor som rör språkundervisningens innehåll och …</t>
+          <t>5 meningar i ett stycke (664 tecken): Kursen innehåller en genomgång av elementär fonetik samt av principerna för tyskt uttal. Den innehåller övningar i att f…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3J5</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1005 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
+          <t>5 meningar i ett stycke (630 tecken): Kursen omfattar dels ett fördjupat studium av tysk formlära och syntax med fokus på kontrastivt viktiga skillnader mella…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>TY1067</t>
+          <t>GTY3J7</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (887 tecken): Kursen är en introduktion till det tyska språket och kulturen i de tysktalande länderna. I kursen ingår läsning av enkla…</t>
+          <t>6 meningar i ett stycke (720 tecken): Inom modulen _Muntlig språkfärdighet_ läggs stor vikt vid att träna den egna språkliga kompetensen med ett brett ordförr…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J7</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>TY1068</t>
+          <t>GTY3J8</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5509,19 +5509,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (923 tecken): I kursen ingår läsning av enklare texter, skriftliga övningar, uttalsövningar och hörövningar av varierande slag. De stu…</t>
+          <t>4 meningar i ett stycke (624 tecken): I kursen studeras dels den tyskspråkiga barn- och ungdomslitteraturens historiska utveckling, dels ett urval texter från…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J8</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>TY1038</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (850 tecken): Kursen omfattar två delmoment, varav det första, språk- och kulturhistoria, fokuserar på huvuddragen av språkutvecklinge…</t>
+          <t>6 meningar i ett stycke (904 tecken): Kursen utgör en introduktion till språkdidaktiken och till de centrala frågor som rör språkundervisningens innehåll och …</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>TY1070</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5563,19 +5563,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1032 tecken): I kursen ingår läsning av längre och mer komplexa tyska texter, skriftliga övningar, uttalsövningar och hörövningar av v…</t>
+          <t>7 meningar i ett stycke (1005 tecken): Kursen innehåller studier av olika aspekter av språklärande varvid diskussion och reflektion kring de didaktiska frågorn…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1067</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5590,44 +5590,152 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (891 tecken): I kursen ingår läsning av längre och mer komplexa tyska texter, skriftliga övningar, uttalsövningar och hörövningar av v…</t>
+          <t>6 meningar i ett stycke (887 tecken): Kursen är en introduktion till det tyska språket och kulturen i de tysktalande länderna. I kursen ingår läsning av enkla…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
+          <t>TY1068</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>7 meningar i ett stycke (923 tecken): I kursen ingår läsning av enklare texter, skriftliga övningar, uttalsövningar och hörövningar av varierande slag. De stu…</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>TY1069</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>5 meningar i ett stycke (850 tecken): Kursen omfattar två delmoment, varav det första, språk- och kulturhistoria, fokuserar på huvuddragen av språkutvecklinge…</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>TY1070</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>7 meningar i ett stycke (1032 tecken): I kursen ingår läsning av längre och mer komplexa tyska texter, skriftliga övningar, uttalsövningar och hörövningar av v…</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>TY1071</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>6 meningar i ett stycke (891 tecken): I kursen ingår läsning av längre och mer komplexa tyska texter, skriftliga övningar, uttalsövningar och hörövningar av v…</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
           <t>TY2007</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Ostyckad textmassa</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
         <is>
           <t>5 meningar i ett stycke (486 tecken): Examensarbetet består av en uppsats som kan ha antingen språk- eller litteraturvetenskaplig inriktning. Inriktning och ä…</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E192"/>
+  <autoFilter ref="A1:E196"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6011,6 +6119,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
